--- a/MIS3371 Contribution Tracker.xlsx
+++ b/MIS3371 Contribution Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/cnguy231_cougarnet_uh_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A17A4CE-04BC-4567-A110-33AB4F329825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40E8F8A2-DA21-4126-A916-F76A6FD7EBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Team Member</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>Sept 16 - Live Build</t>
+  </si>
+  <si>
+    <t>09/21 - Live Build: CSS</t>
+  </si>
+  <si>
+    <t>09/23 - Attendence</t>
   </si>
   <si>
     <t>Lana Tran</t>
@@ -142,7 +148,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -180,11 +186,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -214,6 +231,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -550,13 +573,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7064EB42-CD23-49CB-9B54-70C1C4D8618F}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="8" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="78.95" thickBot="1">
+    <row r="1" spans="1:9" ht="78.95" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,11 +601,16 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="26.45" thickBot="1">
+    <row r="2" spans="1:9" ht="26.45" thickBot="1">
       <c r="A2" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="7">
         <v>100</v>
@@ -602,11 +630,16 @@
       <c r="G2" s="8">
         <v>100</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="5">
+        <v>100</v>
+      </c>
+      <c r="I2" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="26.45" thickBot="1">
+    <row r="3" spans="1:9" ht="26.45" thickBot="1">
       <c r="A3" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="7">
         <v>100</v>
@@ -626,11 +659,16 @@
       <c r="G3" s="8">
         <v>100</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="5">
+        <v>100</v>
+      </c>
+      <c r="I3" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="26.45" thickBot="1">
+    <row r="4" spans="1:9" ht="26.45" thickBot="1">
       <c r="A4" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7">
         <v>100</v>
@@ -650,11 +688,16 @@
       <c r="G4" s="8">
         <v>100</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5">
+        <v>100</v>
+      </c>
+      <c r="I4" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="26.45" thickBot="1">
+    <row r="5" spans="1:9" ht="26.45" thickBot="1">
       <c r="A5" s="9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
@@ -674,11 +717,16 @@
       <c r="G5" s="8">
         <v>100</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5">
+        <v>100</v>
+      </c>
+      <c r="I5" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="26.45" thickBot="1">
+    <row r="6" spans="1:9" ht="26.45" thickBot="1">
       <c r="A6" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="7">
         <v>100</v>
@@ -698,9 +746,14 @@
       <c r="G6" s="8">
         <v>100</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5">
+        <v>100</v>
+      </c>
+      <c r="I6" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1">
+    <row r="7" spans="1:9" ht="15" thickBot="1">
       <c r="A7" s="5"/>
       <c r="B7" s="10"/>
       <c r="C7" s="5"/>
@@ -709,6 +762,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -716,23 +770,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D90AFCFB7A108C4F8F8BA976CF505DEC" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd2c722d48fef0d4ecf736b13d623b42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41165478-3f5a-49d8-b2c1-4a6763303165" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b6d5bfc7d9d23387cb55f9b459df9728" ns3:_="">
     <xsd:import namespace="41165478-3f5a-49d8-b2c1-4a6763303165"/>
@@ -882,14 +919,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
 </file>
--- a/MIS3371 Contribution Tracker.xlsx
+++ b/MIS3371 Contribution Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/cnguy231_cougarnet_uh_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40E8F8A2-DA21-4126-A916-F76A6FD7EBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A17A4CE-04BC-4567-A110-33AB4F329825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Team Member</t>
   </si>
@@ -60,12 +60,6 @@
   </si>
   <si>
     <t>Sept 16 - Live Build</t>
-  </si>
-  <si>
-    <t>09/21 - Live Build: CSS</t>
-  </si>
-  <si>
-    <t>09/23 - Attendence</t>
   </si>
   <si>
     <t>Lana Tran</t>
@@ -148,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -186,22 +180,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -231,12 +214,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,13 +550,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7064EB42-CD23-49CB-9B54-70C1C4D8618F}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="8" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="78.95" thickBot="1">
+    <row r="1" spans="1:8" ht="78.95" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,159 +578,129 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" ht="26.45" thickBot="1">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="B2" s="7">
+        <v>100</v>
+      </c>
+      <c r="C2" s="7">
+        <v>100</v>
+      </c>
+      <c r="D2" s="7">
+        <v>100</v>
+      </c>
+      <c r="E2" s="7">
+        <v>100</v>
+      </c>
+      <c r="F2" s="7">
+        <v>100</v>
+      </c>
+      <c r="G2" s="8">
+        <v>100</v>
+      </c>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" ht="26.45" thickBot="1">
+      <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
+      <c r="B3" s="7">
+        <v>100</v>
+      </c>
+      <c r="C3" s="7">
+        <v>100</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7">
+        <v>100</v>
+      </c>
+      <c r="F3" s="7">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8">
+        <v>100</v>
+      </c>
+      <c r="H3" s="5"/>
     </row>
-    <row r="2" spans="1:9" ht="26.45" thickBot="1">
-      <c r="A2" s="6" t="s">
+    <row r="4" spans="1:8" ht="26.45" thickBot="1">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7">
-        <v>100</v>
-      </c>
-      <c r="C2" s="7">
-        <v>100</v>
-      </c>
-      <c r="D2" s="7">
-        <v>100</v>
-      </c>
-      <c r="E2" s="7">
-        <v>100</v>
-      </c>
-      <c r="F2" s="7">
-        <v>100</v>
-      </c>
-      <c r="G2" s="8">
-        <v>100</v>
-      </c>
-      <c r="H2" s="5">
-        <v>100</v>
-      </c>
-      <c r="I2" s="12">
-        <v>100</v>
-      </c>
+      <c r="B4" s="7">
+        <v>100</v>
+      </c>
+      <c r="C4" s="7">
+        <v>100</v>
+      </c>
+      <c r="D4" s="7">
+        <v>100</v>
+      </c>
+      <c r="E4" s="7">
+        <v>100</v>
+      </c>
+      <c r="F4" s="7">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8">
+        <v>100</v>
+      </c>
+      <c r="H4" s="5"/>
     </row>
-    <row r="3" spans="1:9" ht="26.45" thickBot="1">
-      <c r="A3" s="9" t="s">
+    <row r="5" spans="1:8" ht="26.45" thickBot="1">
+      <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7">
-        <v>100</v>
-      </c>
-      <c r="C3" s="7">
-        <v>100</v>
-      </c>
-      <c r="D3" s="7">
-        <v>100</v>
-      </c>
-      <c r="E3" s="7">
-        <v>100</v>
-      </c>
-      <c r="F3" s="7">
-        <v>100</v>
-      </c>
-      <c r="G3" s="8">
-        <v>100</v>
-      </c>
-      <c r="H3" s="5">
-        <v>100</v>
-      </c>
-      <c r="I3" s="12">
-        <v>100</v>
-      </c>
+      <c r="B5" s="7">
+        <v>100</v>
+      </c>
+      <c r="C5" s="7">
+        <v>100</v>
+      </c>
+      <c r="D5" s="7">
+        <v>100</v>
+      </c>
+      <c r="E5" s="7">
+        <v>100</v>
+      </c>
+      <c r="F5" s="7">
+        <v>100</v>
+      </c>
+      <c r="G5" s="8">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5"/>
     </row>
-    <row r="4" spans="1:9" ht="26.45" thickBot="1">
-      <c r="A4" s="6" t="s">
+    <row r="6" spans="1:8" ht="26.45" thickBot="1">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="7">
-        <v>100</v>
-      </c>
-      <c r="C4" s="7">
-        <v>100</v>
-      </c>
-      <c r="D4" s="7">
-        <v>100</v>
-      </c>
-      <c r="E4" s="7">
-        <v>100</v>
-      </c>
-      <c r="F4" s="7">
-        <v>100</v>
-      </c>
-      <c r="G4" s="8">
-        <v>100</v>
-      </c>
-      <c r="H4" s="5">
-        <v>100</v>
-      </c>
-      <c r="I4" s="12">
-        <v>100</v>
-      </c>
+      <c r="B6" s="7">
+        <v>100</v>
+      </c>
+      <c r="C6" s="7">
+        <v>100</v>
+      </c>
+      <c r="D6" s="7">
+        <v>100</v>
+      </c>
+      <c r="E6" s="7">
+        <v>100</v>
+      </c>
+      <c r="F6" s="7">
+        <v>100</v>
+      </c>
+      <c r="G6" s="8">
+        <v>100</v>
+      </c>
+      <c r="H6" s="5"/>
     </row>
-    <row r="5" spans="1:9" ht="26.45" thickBot="1">
-      <c r="A5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7">
-        <v>100</v>
-      </c>
-      <c r="C5" s="7">
-        <v>100</v>
-      </c>
-      <c r="D5" s="7">
-        <v>100</v>
-      </c>
-      <c r="E5" s="7">
-        <v>100</v>
-      </c>
-      <c r="F5" s="7">
-        <v>100</v>
-      </c>
-      <c r="G5" s="8">
-        <v>100</v>
-      </c>
-      <c r="H5" s="5">
-        <v>100</v>
-      </c>
-      <c r="I5" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="26.45" thickBot="1">
-      <c r="A6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="7">
-        <v>100</v>
-      </c>
-      <c r="C6" s="7">
-        <v>100</v>
-      </c>
-      <c r="D6" s="7">
-        <v>100</v>
-      </c>
-      <c r="E6" s="7">
-        <v>100</v>
-      </c>
-      <c r="F6" s="7">
-        <v>100</v>
-      </c>
-      <c r="G6" s="8">
-        <v>100</v>
-      </c>
-      <c r="H6" s="5">
-        <v>100</v>
-      </c>
-      <c r="I6" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" thickBot="1">
+    <row r="7" spans="1:8" ht="15" thickBot="1">
       <c r="A7" s="5"/>
       <c r="B7" s="10"/>
       <c r="C7" s="5"/>
@@ -762,7 +709,6 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -770,6 +716,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D90AFCFB7A108C4F8F8BA976CF505DEC" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd2c722d48fef0d4ecf736b13d623b42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41165478-3f5a-49d8-b2c1-4a6763303165" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b6d5bfc7d9d23387cb55f9b459df9728" ns3:_="">
     <xsd:import namespace="41165478-3f5a-49d8-b2c1-4a6763303165"/>
@@ -919,31 +882,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
 </file>
--- a/MIS3371 Contribution Tracker.xlsx
+++ b/MIS3371 Contribution Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/cnguy231_cougarnet_uh_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04A82DC7-1E8B-4AC3-B4E2-57BF05D01002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40E8F8A2-DA21-4126-A916-F76A6FD7EBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Team Member</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>09/21 - Live Build: CSS</t>
+  </si>
+  <si>
+    <t>09/23 - Attendence</t>
   </si>
   <si>
     <t>Lana Tran</t>
@@ -198,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -232,6 +235,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,11 +604,13 @@
       <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11"/>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="26.45" thickBot="1">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="7">
         <v>100</v>
@@ -623,12 +631,15 @@
         <v>100</v>
       </c>
       <c r="H2" s="5">
+        <v>100</v>
+      </c>
+      <c r="I2" s="12">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.45" thickBot="1">
       <c r="A3" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="7">
         <v>100</v>
@@ -649,12 +660,15 @@
         <v>100</v>
       </c>
       <c r="H3" s="5">
+        <v>100</v>
+      </c>
+      <c r="I3" s="12">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.45" thickBot="1">
       <c r="A4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7">
         <v>100</v>
@@ -675,12 +689,15 @@
         <v>100</v>
       </c>
       <c r="H4" s="5">
+        <v>100</v>
+      </c>
+      <c r="I4" s="12">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.45" thickBot="1">
       <c r="A5" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
@@ -701,12 +718,15 @@
         <v>100</v>
       </c>
       <c r="H5" s="5">
+        <v>100</v>
+      </c>
+      <c r="I5" s="12">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.45" thickBot="1">
       <c r="A6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="7">
         <v>100</v>
@@ -727,6 +747,9 @@
         <v>100</v>
       </c>
       <c r="H6" s="5">
+        <v>100</v>
+      </c>
+      <c r="I6" s="12">
         <v>100</v>
       </c>
     </row>
@@ -747,23 +770,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D90AFCFB7A108C4F8F8BA976CF505DEC" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd2c722d48fef0d4ecf736b13d623b42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41165478-3f5a-49d8-b2c1-4a6763303165" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b6d5bfc7d9d23387cb55f9b459df9728" ns3:_="">
     <xsd:import namespace="41165478-3f5a-49d8-b2c1-4a6763303165"/>
@@ -913,8 +919,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -922,5 +945,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
 </file>
--- a/MIS3371 Contribution Tracker.xlsx
+++ b/MIS3371 Contribution Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/cnguy231_cougarnet_uh_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e1vej\projects\Team-4-TPS-Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40E8F8A2-DA21-4126-A916-F76A6FD7EBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAB65BE-24E3-40EB-BCD0-AE136E8B2C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Team Member</t>
   </si>
@@ -81,13 +81,22 @@
   </si>
   <si>
     <t>Kim Nguyen</t>
+  </si>
+  <si>
+    <t>09/28 - Participation</t>
+  </si>
+  <si>
+    <t>09/30 - Participation</t>
+  </si>
+  <si>
+    <t>10/5 - Participation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,13 +582,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7064EB42-CD23-49CB-9B54-70C1C4D8618F}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="78.95" thickBot="1">
+    <row r="1" spans="1:12" ht="66.400000000000006" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -607,8 +616,17 @@
       <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="26.45" thickBot="1">
+    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -636,8 +654,17 @@
       <c r="I2" s="12">
         <v>100</v>
       </c>
+      <c r="J2" s="12">
+        <v>100</v>
+      </c>
+      <c r="K2" s="12">
+        <v>100</v>
+      </c>
+      <c r="L2" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="26.45" thickBot="1">
+    <row r="3" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
@@ -665,8 +692,17 @@
       <c r="I3" s="12">
         <v>100</v>
       </c>
+      <c r="J3" s="12">
+        <v>100</v>
+      </c>
+      <c r="K3" s="12">
+        <v>100</v>
+      </c>
+      <c r="L3" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" ht="26.45" thickBot="1">
+    <row r="4" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
@@ -694,8 +730,17 @@
       <c r="I4" s="12">
         <v>100</v>
       </c>
+      <c r="J4" s="12">
+        <v>100</v>
+      </c>
+      <c r="K4" s="12">
+        <v>100</v>
+      </c>
+      <c r="L4" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" ht="26.45" thickBot="1">
+    <row r="5" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -723,8 +768,17 @@
       <c r="I5" s="12">
         <v>100</v>
       </c>
+      <c r="J5" s="12">
+        <v>100</v>
+      </c>
+      <c r="K5" s="12">
+        <v>100</v>
+      </c>
+      <c r="L5" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" ht="26.45" thickBot="1">
+    <row r="6" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
@@ -752,8 +806,17 @@
       <c r="I6" s="12">
         <v>100</v>
       </c>
+      <c r="J6" s="12">
+        <v>100</v>
+      </c>
+      <c r="K6" s="12">
+        <v>100</v>
+      </c>
+      <c r="L6" s="12">
+        <v>100</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" ht="15" thickBot="1">
+    <row r="7" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="5"/>
       <c r="B7" s="10"/>
       <c r="C7" s="5"/>
@@ -763,6 +826,9 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -920,14 +986,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -936,14 +994,46 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="41165478-3f5a-49d8-b2c1-4a6763303165"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="41165478-3f5a-49d8-b2c1-4a6763303165"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MIS3371 Contribution Tracker.xlsx
+++ b/MIS3371 Contribution Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e1vej\projects\Team-4-TPS-Repo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/cnguy231_cougarnet_uh_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAB65BE-24E3-40EB-BCD0-AE136E8B2C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9D62741-4A63-47AA-89AC-771C097AF1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
+    <workbookView minimized="1" xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Team Member</t>
   </si>
@@ -68,6 +68,12 @@
     <t>09/23 - Attendence</t>
   </si>
   <si>
+    <t>10/5/2026 - Live Build</t>
+  </si>
+  <si>
+    <t>10/7/2026 - Live Build</t>
+  </si>
+  <si>
     <t>Lana Tran</t>
   </si>
   <si>
@@ -81,22 +87,13 @@
   </si>
   <si>
     <t>Kim Nguyen</t>
-  </si>
-  <si>
-    <t>09/28 - Participation</t>
-  </si>
-  <si>
-    <t>09/30 - Participation</t>
-  </si>
-  <si>
-    <t>10/5 - Participation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +132,14 @@
       <color rgb="FF273540"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -210,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -248,6 +253,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,13 +588,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7064EB42-CD23-49CB-9B54-70C1C4D8618F}">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="7" max="7" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="66.400000000000006" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="78.95" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,207 +624,189 @@
       <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="26.45" thickBot="1">
+      <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="7">
+        <v>100</v>
+      </c>
+      <c r="C2" s="7">
+        <v>100</v>
+      </c>
+      <c r="D2" s="7">
+        <v>100</v>
+      </c>
+      <c r="E2" s="7">
+        <v>100</v>
+      </c>
+      <c r="F2" s="7">
+        <v>100</v>
+      </c>
+      <c r="G2" s="8">
+        <v>100</v>
+      </c>
+      <c r="H2" s="5">
+        <v>100</v>
+      </c>
+      <c r="I2" s="12">
+        <v>100</v>
+      </c>
+      <c r="J2" s="12">
+        <v>100</v>
+      </c>
+      <c r="K2" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="26.45" thickBot="1">
+      <c r="A3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7">
+        <v>100</v>
+      </c>
+      <c r="C3" s="7">
+        <v>100</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7">
+        <v>100</v>
+      </c>
+      <c r="F3" s="7">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8">
+        <v>100</v>
+      </c>
+      <c r="H3" s="5">
+        <v>100</v>
+      </c>
+      <c r="I3" s="12">
+        <v>100</v>
+      </c>
+      <c r="J3" s="12">
+        <v>100</v>
+      </c>
+      <c r="K3" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="26.45" thickBot="1">
+      <c r="A4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7">
+        <v>100</v>
+      </c>
+      <c r="C4" s="7">
+        <v>100</v>
+      </c>
+      <c r="D4" s="7">
+        <v>100</v>
+      </c>
+      <c r="E4" s="7">
+        <v>100</v>
+      </c>
+      <c r="F4" s="7">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8">
+        <v>100</v>
+      </c>
+      <c r="H4" s="5">
+        <v>100</v>
+      </c>
+      <c r="I4" s="12">
+        <v>100</v>
+      </c>
+      <c r="J4" s="12">
+        <v>100</v>
+      </c>
+      <c r="K4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="26.45" thickBot="1">
+      <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="B5" s="7">
+        <v>100</v>
+      </c>
+      <c r="C5" s="7">
+        <v>100</v>
+      </c>
+      <c r="D5" s="7">
+        <v>100</v>
+      </c>
+      <c r="E5" s="7">
+        <v>100</v>
+      </c>
+      <c r="F5" s="7">
+        <v>100</v>
+      </c>
+      <c r="G5" s="8">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5">
+        <v>100</v>
+      </c>
+      <c r="I5" s="12">
+        <v>100</v>
+      </c>
+      <c r="J5" s="12">
+        <v>100</v>
+      </c>
+      <c r="K5" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="26.45" thickBot="1">
+      <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="11" t="s">
-        <v>16</v>
+      <c r="B6" s="7">
+        <v>100</v>
+      </c>
+      <c r="C6" s="7">
+        <v>100</v>
+      </c>
+      <c r="D6" s="7">
+        <v>100</v>
+      </c>
+      <c r="E6" s="7">
+        <v>100</v>
+      </c>
+      <c r="F6" s="7">
+        <v>100</v>
+      </c>
+      <c r="G6" s="8">
+        <v>100</v>
+      </c>
+      <c r="H6" s="5">
+        <v>100</v>
+      </c>
+      <c r="I6" s="12">
+        <v>100</v>
+      </c>
+      <c r="J6" s="12">
+        <v>100</v>
+      </c>
+      <c r="K6" s="12">
+        <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7">
-        <v>100</v>
-      </c>
-      <c r="C2" s="7">
-        <v>100</v>
-      </c>
-      <c r="D2" s="7">
-        <v>100</v>
-      </c>
-      <c r="E2" s="7">
-        <v>100</v>
-      </c>
-      <c r="F2" s="7">
-        <v>100</v>
-      </c>
-      <c r="G2" s="8">
-        <v>100</v>
-      </c>
-      <c r="H2" s="5">
-        <v>100</v>
-      </c>
-      <c r="I2" s="12">
-        <v>100</v>
-      </c>
-      <c r="J2" s="12">
-        <v>100</v>
-      </c>
-      <c r="K2" s="12">
-        <v>100</v>
-      </c>
-      <c r="L2" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7">
-        <v>100</v>
-      </c>
-      <c r="C3" s="7">
-        <v>100</v>
-      </c>
-      <c r="D3" s="7">
-        <v>100</v>
-      </c>
-      <c r="E3" s="7">
-        <v>100</v>
-      </c>
-      <c r="F3" s="7">
-        <v>100</v>
-      </c>
-      <c r="G3" s="8">
-        <v>100</v>
-      </c>
-      <c r="H3" s="5">
-        <v>100</v>
-      </c>
-      <c r="I3" s="12">
-        <v>100</v>
-      </c>
-      <c r="J3" s="12">
-        <v>100</v>
-      </c>
-      <c r="K3" s="12">
-        <v>100</v>
-      </c>
-      <c r="L3" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="7">
-        <v>100</v>
-      </c>
-      <c r="C4" s="7">
-        <v>100</v>
-      </c>
-      <c r="D4" s="7">
-        <v>100</v>
-      </c>
-      <c r="E4" s="7">
-        <v>100</v>
-      </c>
-      <c r="F4" s="7">
-        <v>100</v>
-      </c>
-      <c r="G4" s="8">
-        <v>100</v>
-      </c>
-      <c r="H4" s="5">
-        <v>100</v>
-      </c>
-      <c r="I4" s="12">
-        <v>100</v>
-      </c>
-      <c r="J4" s="12">
-        <v>100</v>
-      </c>
-      <c r="K4" s="12">
-        <v>100</v>
-      </c>
-      <c r="L4" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7">
-        <v>100</v>
-      </c>
-      <c r="C5" s="7">
-        <v>100</v>
-      </c>
-      <c r="D5" s="7">
-        <v>100</v>
-      </c>
-      <c r="E5" s="7">
-        <v>100</v>
-      </c>
-      <c r="F5" s="7">
-        <v>100</v>
-      </c>
-      <c r="G5" s="8">
-        <v>100</v>
-      </c>
-      <c r="H5" s="5">
-        <v>100</v>
-      </c>
-      <c r="I5" s="12">
-        <v>100</v>
-      </c>
-      <c r="J5" s="12">
-        <v>100</v>
-      </c>
-      <c r="K5" s="12">
-        <v>100</v>
-      </c>
-      <c r="L5" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="7">
-        <v>100</v>
-      </c>
-      <c r="C6" s="7">
-        <v>100</v>
-      </c>
-      <c r="D6" s="7">
-        <v>100</v>
-      </c>
-      <c r="E6" s="7">
-        <v>100</v>
-      </c>
-      <c r="F6" s="7">
-        <v>100</v>
-      </c>
-      <c r="G6" s="8">
-        <v>100</v>
-      </c>
-      <c r="H6" s="5">
-        <v>100</v>
-      </c>
-      <c r="I6" s="12">
-        <v>100</v>
-      </c>
-      <c r="J6" s="12">
-        <v>100</v>
-      </c>
-      <c r="K6" s="12">
-        <v>100</v>
-      </c>
-      <c r="L6" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" ht="15" thickBot="1">
       <c r="A7" s="5"/>
       <c r="B7" s="10"/>
       <c r="C7" s="5"/>
@@ -826,9 +816,6 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -836,6 +823,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D90AFCFB7A108C4F8F8BA976CF505DEC" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd2c722d48fef0d4ecf736b13d623b42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="41165478-3f5a-49d8-b2c1-4a6763303165" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b6d5bfc7d9d23387cb55f9b459df9728" ns3:_="">
     <xsd:import namespace="41165478-3f5a-49d8-b2c1-4a6763303165"/>
@@ -985,55 +989,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="41165478-3f5a-49d8-b2c1-4a6763303165"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="41165478-3f5a-49d8-b2c1-4a6763303165"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
 </file>
--- a/MIS3371 Contribution Tracker.xlsx
+++ b/MIS3371 Contribution Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/cnguy231_cougarnet_uh_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc948785acc72d1c/Documents/GitHub/Team-4-TPS-Repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9D62741-4A63-47AA-89AC-771C097AF1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{F9D62741-4A63-47AA-89AC-771C097AF1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE08EDBB-AE71-4D6E-B378-FD52518AA2BE}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Team Member</t>
   </si>
@@ -62,18 +62,6 @@
     <t>Sept 16 - Live Build</t>
   </si>
   <si>
-    <t>09/21 - Live Build: CSS</t>
-  </si>
-  <si>
-    <t>09/23 - Attendence</t>
-  </si>
-  <si>
-    <t>10/5/2026 - Live Build</t>
-  </si>
-  <si>
-    <t>10/7/2026 - Live Build</t>
-  </si>
-  <si>
     <t>Lana Tran</t>
   </si>
   <si>
@@ -88,12 +76,27 @@
   <si>
     <t>Kim Nguyen</t>
   </si>
+  <si>
+    <t>Milestone 2</t>
+  </si>
+  <si>
+    <t>Sept 21 - Live Build: CSS</t>
+  </si>
+  <si>
+    <t>Sept 23 - Attendence</t>
+  </si>
+  <si>
+    <t>Oct 05 - Live Build</t>
+  </si>
+  <si>
+    <t>Oct 07 - Live Build</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,12 +126,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF1F2328"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF273540"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -140,6 +137,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -162,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -171,43 +175,113 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFD1D9E0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD1D9E0"/>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFD1D9E0"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -215,50 +289,601 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF273540"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -269,6 +894,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07BEA054-C795-4777-AAFF-CDB4299AA873}" name="Table1" displayName="Table1" ref="A1:L6" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+  <autoFilter ref="A1:L6" xr:uid="{07BEA054-C795-4777-AAFF-CDB4299AA873}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{A65ABBBF-7509-4090-B388-D93370E614C4}" name="Team Member" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{F848FAEB-0959-4D2B-A78B-38BC68356D1E}" name="Sept 3 - TPS Workflow" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{EECB050E-121B-4C74-ACE4-2C1BDF0C712D}" name="Sept 5 - Out of Class, GIthub Setup" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{F1E5AB18-D5D1-47EC-A49E-99FF95F16833}" name="Sept 8 - Milestone 1 Proposal" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{06DD9926-494B-4F64-B25C-12F11DBB1FA3}" name="Sept 10 - Live Build: HTML Structure" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{05EC3925-9BE6-4BC6-93A2-E00D1EA4A52D}" name="Sept 13 - Milestone 1" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{093DDED9-10EC-4E24-853D-4DA3DC3386CF}" name="Sept 16 - Live Build" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{43596F43-5D27-445C-B70F-C83EA60D1D3C}" name="Sept 21 - Live Build: CSS" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{FD370EDC-45B1-4F59-B34F-7EB5F5A31B61}" name="Sept 23 - Attendence" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{747D1861-0A87-45FD-8A38-1CFBD1346FAE}" name="Oct 05 - Live Build" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{4EE46AEB-1F09-418B-A091-F57229CF23A1}" name="Oct 07 - Live Build" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{E293BF80-E4A8-4EA5-AE62-A9E9D21F797A}" name="Milestone 2" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,255 +1234,265 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7064EB42-CD23-49CB-9B54-70C1C4D8618F}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="14" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="78.95" thickBot="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="12" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="B2" s="2">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="3">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>100</v>
+      </c>
+      <c r="J2" s="2">
+        <v>100</v>
+      </c>
+      <c r="K2" s="2">
+        <v>100</v>
+      </c>
+      <c r="L2" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="B3" s="2">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2">
+        <v>100</v>
+      </c>
+      <c r="E3" s="2">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2">
+        <v>100</v>
+      </c>
+      <c r="G3" s="2">
+        <v>100</v>
+      </c>
+      <c r="H3" s="3">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>100</v>
+      </c>
+      <c r="J3" s="2">
+        <v>100</v>
+      </c>
+      <c r="K3" s="2">
+        <v>100</v>
+      </c>
+      <c r="L3" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="B4" s="2">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100</v>
+      </c>
+      <c r="D4" s="2">
+        <v>100</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2">
+        <v>100</v>
+      </c>
+      <c r="H4" s="3">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>100</v>
+      </c>
+      <c r="J4" s="2">
+        <v>100</v>
+      </c>
+      <c r="K4" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
+      <c r="B5" s="2">
+        <v>100</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2">
+        <v>100</v>
+      </c>
+      <c r="E5" s="2">
+        <v>100</v>
+      </c>
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
+        <v>100</v>
+      </c>
+      <c r="H5" s="3">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>100</v>
+      </c>
+      <c r="J5" s="2">
+        <v>100</v>
+      </c>
+      <c r="K5" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" s="4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="26.45" thickBot="1">
-      <c r="A2" s="6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7">
-        <v>100</v>
-      </c>
-      <c r="C2" s="7">
-        <v>100</v>
-      </c>
-      <c r="D2" s="7">
-        <v>100</v>
-      </c>
-      <c r="E2" s="7">
-        <v>100</v>
-      </c>
-      <c r="F2" s="7">
-        <v>100</v>
-      </c>
-      <c r="G2" s="8">
-        <v>100</v>
-      </c>
-      <c r="H2" s="5">
-        <v>100</v>
-      </c>
-      <c r="I2" s="12">
-        <v>100</v>
-      </c>
-      <c r="J2" s="12">
-        <v>100</v>
-      </c>
-      <c r="K2" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="26.45" thickBot="1">
-      <c r="A3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7">
-        <v>100</v>
-      </c>
-      <c r="C3" s="7">
-        <v>100</v>
-      </c>
-      <c r="D3" s="7">
-        <v>100</v>
-      </c>
-      <c r="E3" s="7">
-        <v>100</v>
-      </c>
-      <c r="F3" s="7">
-        <v>100</v>
-      </c>
-      <c r="G3" s="8">
-        <v>100</v>
-      </c>
-      <c r="H3" s="5">
-        <v>100</v>
-      </c>
-      <c r="I3" s="12">
-        <v>100</v>
-      </c>
-      <c r="J3" s="12">
-        <v>100</v>
-      </c>
-      <c r="K3" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="26.45" thickBot="1">
-      <c r="A4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="7">
-        <v>100</v>
-      </c>
-      <c r="C4" s="7">
-        <v>100</v>
-      </c>
-      <c r="D4" s="7">
-        <v>100</v>
-      </c>
-      <c r="E4" s="7">
-        <v>100</v>
-      </c>
-      <c r="F4" s="7">
-        <v>100</v>
-      </c>
-      <c r="G4" s="8">
-        <v>100</v>
-      </c>
-      <c r="H4" s="5">
-        <v>100</v>
-      </c>
-      <c r="I4" s="12">
-        <v>100</v>
-      </c>
-      <c r="J4" s="12">
-        <v>100</v>
-      </c>
-      <c r="K4" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="26.45" thickBot="1">
-      <c r="A5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="7">
-        <v>100</v>
-      </c>
-      <c r="C5" s="7">
-        <v>100</v>
-      </c>
-      <c r="D5" s="7">
-        <v>100</v>
-      </c>
-      <c r="E5" s="7">
-        <v>100</v>
-      </c>
-      <c r="F5" s="7">
-        <v>100</v>
-      </c>
-      <c r="G5" s="8">
-        <v>100</v>
-      </c>
-      <c r="H5" s="5">
-        <v>100</v>
-      </c>
-      <c r="I5" s="12">
-        <v>100</v>
-      </c>
-      <c r="J5" s="12">
-        <v>100</v>
-      </c>
-      <c r="K5" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="26.45" thickBot="1">
-      <c r="A6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="7">
-        <v>100</v>
-      </c>
-      <c r="C6" s="7">
-        <v>100</v>
-      </c>
-      <c r="D6" s="7">
-        <v>100</v>
-      </c>
-      <c r="E6" s="7">
-        <v>100</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="B6" s="8">
+        <v>100</v>
+      </c>
+      <c r="C6" s="8">
+        <v>100</v>
+      </c>
+      <c r="D6" s="8">
+        <v>100</v>
+      </c>
+      <c r="E6" s="8">
+        <v>100</v>
+      </c>
+      <c r="F6" s="8">
         <v>100</v>
       </c>
       <c r="G6" s="8">
         <v>100</v>
       </c>
-      <c r="H6" s="5">
-        <v>100</v>
-      </c>
-      <c r="I6" s="12">
-        <v>100</v>
-      </c>
-      <c r="J6" s="12">
-        <v>100</v>
-      </c>
-      <c r="K6" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="H6" s="9">
+        <v>100</v>
+      </c>
+      <c r="I6" s="8">
+        <v>100</v>
+      </c>
+      <c r="J6" s="8">
+        <v>100</v>
+      </c>
+      <c r="K6" s="8">
+        <v>100</v>
+      </c>
+      <c r="L6" s="10">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -990,13 +1646,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="41165478-3f5a-49d8-b2c1-4a6763303165"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D321C-E5D4-40B4-8EE2-EB514AE9DC35}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="41165478-3f5a-49d8-b2c1-4a6763303165"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>